--- a/요구사항명세서.xlsx
+++ b/요구사항명세서.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9303"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <workbookPr defaultThemeVersion="166925"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dlxod\workspace\capstone\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6212F0B1-E9F6-467E-9CB1-5B60A214320C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="180" yWindow="600" windowWidth="25440" windowHeight="15990"/>
+    <workbookView xWindow="12710" yWindow="0" windowWidth="12980" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="요구사항정의서" sheetId="1" r:id="rId1"/>
@@ -14,20 +20,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="265">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="225">
   <si>
     <t>요구사항명</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -93,10 +91,6 @@
   </si>
   <si>
     <t>최초요청일자</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>로그인</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -161,17 +155,6 @@
     <t>권한 없는 버전 수정 제한</t>
   </si>
   <si>
-    <t>로그인 화면 
-ID/Passwd 인증</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>*이메일/비밀번호 입력 후 로그인 허용
-*로그인 성공 시 프로젝트 리스트 이동 
-*실패 시 오류 메시지 출력</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>사용자 인증</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -213,10 +196,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>REQ_005</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>잘못된 데이터 방지</t>
   </si>
   <si>
@@ -320,15 +299,6 @@
   </si>
   <si>
     <t>REQ_026</t>
-  </si>
-  <si>
-    <t>REQ_027</t>
-  </si>
-  <si>
-    <t>REQ_028</t>
-  </si>
-  <si>
-    <t>REQ_029</t>
   </si>
   <si>
     <t>결과 화면 출력</t>
@@ -431,15 +401,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>REQ_030</t>
-  </si>
-  <si>
-    <t>REQ_031</t>
-  </si>
-  <si>
-    <t>REQ_032</t>
-  </si>
-  <si>
     <t>클러스터링 화면 출력</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -515,173 +476,6 @@
   </si>
   <si>
     <t>*클래스 분포 수 표시 영역 필요</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>인퍼런스/서빙</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>단건 추론 기능</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>결과 검증</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>*저장된 모델로 단일 이미지 추론 수행</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>모델 선택 → 이미지 입력 → 추론 실행</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>*간단한 추론 화면 
-*결과 팝업 필요</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>업로드 파일 검증</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>inference 결과 저장 선택 가능</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>온라인 추론 API 제공</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>외부 시스템 연동</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>*REST API 형태로 예측 요청/응답 제공</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>모델 로드 → 요청 처리 → 응답 반환</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>*API 문서/상태 화면 필요</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>API 인증키, 요청 제한, 
-접근 통제 필요</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>배포 모델 버전 정보 필요</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>실시간 온라인 서빙</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>실서비스 운영</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>*선택된 best model을 온라인 서비스에 
-배포 가능해야 함</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>모델 등록 → 배포 → 상태 관리</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>*배포 상태 화면 필요</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>deploy metadata 저장 필요</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>인증/인가, 모델 접근제어</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>데이터</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>실험 재현성 확보</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>*dataset version 
-*model, code version 
-*hyperparams를 run과 함께 저장</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>run 생성 시 모든 참조 연결</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>*run 상세 화면에 메타정보 표시</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>experiment_runs에 모든 
-FK/JSON 필요</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>결과 추적</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>버전 추적</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>데이터 변경 이력 관리</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>결과 산출물 관리</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>*best model, last model 
-*confusion matrix, embedding, plot 저장</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>*add/delete/edit/relabel 이력 저장</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>run 종료 후 artifact 등록</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>변경 발생 시 log 기록 또는 새 버전 생성</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>*artifact 목록 UI 필요</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>*이력 화면 필요</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>run_artifacts 필요</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>dataset_change_logs 필요</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1189,11 +983,53 @@
   <si>
     <t>REQ_017</t>
   </si>
+  <si>
+    <t>REQ_004</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>로그인 및 회원가입</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>REQ_002</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>로그인 화면
+ID/Passwd 인증</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>신규 회원가입
+ID/Passwd 인증</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>신규 계정 생성, 중복 이메일 검증, 비밀번호 단방향 암호화(해싱) 후 DB 안전 저장.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>사용자 인증 및 접근 제어</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이메일/비밀번호 입력 후 시스템 인증, 세션/토큰 발급 및 유지, 시스템 로그아웃 기능 지원.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>입력값 validation → 사용자 조회 → 인증 → 세션/토큰 발급 (로그아웃 시 세션 폐기)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아이디/비밀번호 입력 필드, [Continue] 버튼, 상단 GNB 내 로그아웃 버튼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="22" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1449,7 +1285,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1548,9 +1384,6 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="14" fontId="17" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
       <protection locked="0"/>
@@ -1579,67 +1412,63 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="14" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="14" fontId="7" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -1955,50 +1784,50 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AC45"/>
-  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:AC38"/>
+  <sheetFormatPr defaultColWidth="8.58203125" defaultRowHeight="16" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="11.375" style="7" customWidth="1"/>
-    <col min="2" max="2" width="12.375" style="7" customWidth="1"/>
-    <col min="3" max="3" width="10.125" style="8" customWidth="1"/>
-    <col min="4" max="4" width="24.625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="8.625" style="8" customWidth="1"/>
+    <col min="1" max="1" width="11.33203125" style="7" customWidth="1"/>
+    <col min="2" max="2" width="12.33203125" style="7" customWidth="1"/>
+    <col min="3" max="3" width="10.08203125" style="8" customWidth="1"/>
+    <col min="4" max="4" width="24.58203125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="8.58203125" style="8" customWidth="1"/>
     <col min="6" max="6" width="6.5" style="8" customWidth="1"/>
     <col min="7" max="8" width="10" style="8" customWidth="1"/>
-    <col min="9" max="9" width="15.625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="15.58203125" style="1" customWidth="1"/>
     <col min="10" max="10" width="28.5" style="1" customWidth="1"/>
-    <col min="11" max="11" width="42.875" style="1" customWidth="1"/>
-    <col min="12" max="12" width="28.875" style="1" customWidth="1"/>
-    <col min="13" max="13" width="26.625" style="1" customWidth="1"/>
-    <col min="14" max="14" width="19.625" style="1" customWidth="1"/>
-    <col min="15" max="15" width="25.375" style="1" customWidth="1"/>
-    <col min="16" max="16" width="20.875" style="1" customWidth="1"/>
-    <col min="17" max="16384" width="8.625" style="1"/>
+    <col min="11" max="11" width="42.83203125" style="1" customWidth="1"/>
+    <col min="12" max="12" width="28.83203125" style="1" customWidth="1"/>
+    <col min="13" max="13" width="26.58203125" style="1" customWidth="1"/>
+    <col min="14" max="14" width="19.58203125" style="1" customWidth="1"/>
+    <col min="15" max="15" width="25.33203125" style="1" customWidth="1"/>
+    <col min="16" max="16" width="20.83203125" style="1" customWidth="1"/>
+    <col min="17" max="16384" width="8.58203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:29" ht="17.5" x14ac:dyDescent="0.45">
       <c r="A1" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" s="9"/>
+    </row>
+    <row r="2" spans="1:29" ht="17.5" x14ac:dyDescent="0.45">
+      <c r="A2" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="9"/>
-    </row>
-    <row r="2" spans="1:29" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A2" s="22" t="s">
-        <v>23</v>
-      </c>
       <c r="B2" s="9"/>
     </row>
-    <row r="3" spans="1:29" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:29" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" s="12" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B3" s="13"/>
       <c r="C3" s="10"/>
@@ -2016,9 +1845,9 @@
       <c r="O3" s="11"/>
       <c r="P3" s="11"/>
     </row>
-    <row r="4" spans="1:29" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:29" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" s="12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="10"/>
@@ -2036,7 +1865,7 @@
       <c r="O4" s="11"/>
       <c r="P4" s="11"/>
     </row>
-    <row r="5" spans="1:29" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:29" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="13"/>
       <c r="B5" s="13"/>
       <c r="C5" s="10"/>
@@ -2053,8 +1882,8 @@
       <c r="N5" s="11"/>
       <c r="O5" s="11"/>
     </row>
-    <row r="6" spans="1:29" ht="9" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="7" spans="1:29" ht="40.5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:29" ht="9" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="7" spans="1:29" ht="48" x14ac:dyDescent="0.45">
       <c r="A7" s="14" t="s">
         <v>5</v>
       </c>
@@ -2068,7 +1897,7 @@
         <v>0</v>
       </c>
       <c r="E7" s="14" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F7" s="14" t="s">
         <v>14</v>
@@ -2098,323 +1927,325 @@
         <v>12</v>
       </c>
       <c r="O7" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="P7" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:29" ht="42.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:29" ht="43" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A8" s="20" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>17</v>
+        <v>216</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>31</v>
+        <v>218</v>
       </c>
       <c r="E8" s="6"/>
       <c r="F8" s="6"/>
       <c r="G8" s="6"/>
       <c r="H8" s="6"/>
       <c r="I8" s="16" t="s">
-        <v>33</v>
+        <v>221</v>
       </c>
       <c r="J8" s="19" t="s">
-        <v>32</v>
+        <v>222</v>
       </c>
       <c r="K8" s="16" t="s">
-        <v>25</v>
+        <v>223</v>
       </c>
       <c r="L8" s="19" t="s">
-        <v>39</v>
-      </c>
-      <c r="M8" s="29" t="s">
-        <v>37</v>
+        <v>224</v>
+      </c>
+      <c r="M8" s="28" t="s">
+        <v>34</v>
       </c>
       <c r="N8" s="17"/>
       <c r="O8" s="17" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P8" s="17"/>
     </row>
-    <row r="9" spans="1:29" ht="42.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:29" ht="43" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A9" s="21"/>
-      <c r="B9" s="45" t="s">
-        <v>27</v>
-      </c>
+      <c r="B9" s="6"/>
       <c r="C9" s="6" t="s">
-        <v>3</v>
+        <v>217</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="E9" s="6"/>
       <c r="F9" s="6"/>
       <c r="G9" s="6"/>
       <c r="H9" s="6"/>
       <c r="I9" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="J9" s="19" t="s">
+        <v>220</v>
+      </c>
+      <c r="K9" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="L9" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="M9" s="28" t="s">
         <v>34</v>
-      </c>
-      <c r="J9" s="19" t="s">
-        <v>231</v>
-      </c>
-      <c r="K9" s="16" t="s">
-        <v>232</v>
-      </c>
-      <c r="L9" s="19" t="s">
-        <v>233</v>
-      </c>
-      <c r="M9" s="29" t="s">
-        <v>28</v>
       </c>
       <c r="N9" s="17"/>
       <c r="O9" s="17" t="s">
-        <v>234</v>
+        <v>25</v>
       </c>
       <c r="P9" s="17"/>
     </row>
-    <row r="10" spans="1:29" ht="57.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:29" ht="58" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A10" s="21"/>
-      <c r="B10" s="46"/>
+      <c r="B10" s="48" t="s">
+        <v>26</v>
+      </c>
       <c r="C10" s="6" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>235</v>
+        <v>180</v>
       </c>
       <c r="E10" s="6"/>
       <c r="F10" s="6"/>
       <c r="G10" s="6"/>
       <c r="H10" s="6"/>
       <c r="I10" s="16" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="J10" s="19" t="s">
-        <v>236</v>
+        <v>181</v>
       </c>
       <c r="K10" s="16" t="s">
-        <v>237</v>
+        <v>182</v>
       </c>
       <c r="L10" s="19" t="s">
-        <v>238</v>
-      </c>
-      <c r="M10" s="29" t="s">
-        <v>29</v>
+        <v>183</v>
+      </c>
+      <c r="M10" s="28" t="s">
+        <v>27</v>
       </c>
       <c r="N10" s="17"/>
       <c r="O10" s="17" t="s">
-        <v>239</v>
+        <v>184</v>
       </c>
       <c r="P10" s="17"/>
     </row>
-    <row r="11" spans="1:29" ht="42.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="36"/>
-      <c r="B11" s="45" t="s">
-        <v>201</v>
-      </c>
+    <row r="11" spans="1:29" ht="43" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A11" s="21"/>
+      <c r="B11" s="49"/>
       <c r="C11" s="6" t="s">
-        <v>42</v>
+        <v>4</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="E11" s="6"/>
       <c r="F11" s="6"/>
       <c r="G11" s="6"/>
       <c r="H11" s="6"/>
       <c r="I11" s="16" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="J11" s="19" t="s">
-        <v>177</v>
-      </c>
-      <c r="K11" s="19" t="s">
-        <v>178</v>
+        <v>186</v>
+      </c>
+      <c r="K11" s="16" t="s">
+        <v>187</v>
       </c>
       <c r="L11" s="19" t="s">
-        <v>176</v>
-      </c>
-      <c r="M11" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="N11" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="O11" s="30" t="s">
-        <v>179</v>
-      </c>
-      <c r="P11" s="23"/>
-    </row>
-    <row r="12" spans="1:29" ht="42.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="36"/>
-      <c r="B12" s="46"/>
+        <v>188</v>
+      </c>
+      <c r="M11" s="28" t="s">
+        <v>28</v>
+      </c>
+      <c r="N11" s="17"/>
+      <c r="O11" s="17" t="s">
+        <v>189</v>
+      </c>
+      <c r="P11" s="17"/>
+    </row>
+    <row r="12" spans="1:29" ht="43" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A12" s="21"/>
+      <c r="B12" s="48" t="s">
+        <v>151</v>
+      </c>
       <c r="C12" s="6" t="s">
-        <v>252</v>
+        <v>215</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>180</v>
+        <v>125</v>
       </c>
       <c r="E12" s="6"/>
       <c r="F12" s="6"/>
       <c r="G12" s="6"/>
       <c r="H12" s="6"/>
       <c r="I12" s="16" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J12" s="19" t="s">
-        <v>181</v>
+        <v>127</v>
       </c>
       <c r="K12" s="19" t="s">
-        <v>182</v>
+        <v>128</v>
       </c>
       <c r="L12" s="19" t="s">
-        <v>183</v>
+        <v>126</v>
       </c>
       <c r="M12" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="N12" s="18"/>
-      <c r="O12" s="31" t="s">
-        <v>184</v>
+        <v>37</v>
+      </c>
+      <c r="N12" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="O12" s="29" t="s">
+        <v>129</v>
       </c>
       <c r="P12" s="23"/>
     </row>
-    <row r="13" spans="1:29" ht="42.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="36"/>
-      <c r="B13" s="47"/>
+    <row r="13" spans="1:29" ht="43" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A13" s="21"/>
+      <c r="B13" s="49"/>
       <c r="C13" s="6" t="s">
-        <v>253</v>
+        <v>202</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>185</v>
+        <v>130</v>
       </c>
       <c r="E13" s="6"/>
       <c r="F13" s="6"/>
       <c r="G13" s="6"/>
       <c r="H13" s="6"/>
       <c r="I13" s="16" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J13" s="19" t="s">
-        <v>186</v>
+        <v>131</v>
       </c>
       <c r="K13" s="19" t="s">
-        <v>248</v>
+        <v>132</v>
       </c>
       <c r="L13" s="19" t="s">
-        <v>187</v>
+        <v>133</v>
       </c>
       <c r="M13" s="18" t="s">
-        <v>44</v>
-      </c>
-      <c r="N13" s="18" t="s">
-        <v>45</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="N13" s="18"/>
       <c r="O13" s="30" t="s">
-        <v>188</v>
-      </c>
-      <c r="P13" s="18"/>
-    </row>
-    <row r="14" spans="1:29" ht="59.1" customHeight="1" x14ac:dyDescent="0.3">
+        <v>134</v>
+      </c>
+      <c r="P13" s="23"/>
+    </row>
+    <row r="14" spans="1:29" ht="59.15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A14" s="21"/>
-      <c r="B14" s="45" t="s">
-        <v>190</v>
-      </c>
+      <c r="B14" s="50"/>
       <c r="C14" s="6" t="s">
-        <v>254</v>
+        <v>203</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>191</v>
+        <v>135</v>
       </c>
       <c r="E14" s="6"/>
       <c r="F14" s="6"/>
       <c r="G14" s="6"/>
       <c r="H14" s="6"/>
       <c r="I14" s="16" t="s">
-        <v>192</v>
+        <v>39</v>
       </c>
       <c r="J14" s="19" t="s">
-        <v>241</v>
-      </c>
-      <c r="K14" s="16" t="s">
-        <v>240</v>
+        <v>136</v>
+      </c>
+      <c r="K14" s="19" t="s">
+        <v>198</v>
       </c>
       <c r="L14" s="19" t="s">
-        <v>193</v>
-      </c>
-      <c r="M14" s="48"/>
-      <c r="N14" s="18"/>
-      <c r="O14" s="30" t="s">
-        <v>194</v>
-      </c>
-      <c r="P14" s="49"/>
-    </row>
-    <row r="15" spans="1:29" ht="59.1" customHeight="1" x14ac:dyDescent="0.3">
+        <v>137</v>
+      </c>
+      <c r="M14" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="N14" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="O14" s="29" t="s">
+        <v>138</v>
+      </c>
+      <c r="P14" s="18"/>
+    </row>
+    <row r="15" spans="1:29" ht="59.15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A15" s="21"/>
-      <c r="B15" s="47"/>
+      <c r="B15" s="48" t="s">
+        <v>140</v>
+      </c>
       <c r="C15" s="6" t="s">
-        <v>255</v>
-      </c>
-      <c r="D15" s="37" t="s">
-        <v>195</v>
-      </c>
-      <c r="E15" s="41"/>
-      <c r="F15" s="41"/>
-      <c r="G15" s="41"/>
-      <c r="H15" s="41"/>
-      <c r="I15" s="38"/>
-      <c r="J15" s="39" t="s">
-        <v>196</v>
-      </c>
-      <c r="K15" s="38" t="s">
-        <v>197</v>
-      </c>
-      <c r="L15" s="39" t="s">
-        <v>198</v>
-      </c>
-      <c r="M15" s="18"/>
-      <c r="N15" s="40"/>
-      <c r="O15" s="32" t="s">
-        <v>199</v>
-      </c>
-      <c r="P15" s="50"/>
-    </row>
-    <row r="16" spans="1:29" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+        <v>204</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="E15" s="6"/>
+      <c r="F15" s="6"/>
+      <c r="G15" s="6"/>
+      <c r="H15" s="6"/>
+      <c r="I15" s="16" t="s">
+        <v>142</v>
+      </c>
+      <c r="J15" s="19" t="s">
+        <v>191</v>
+      </c>
+      <c r="K15" s="16" t="s">
+        <v>190</v>
+      </c>
+      <c r="L15" s="19" t="s">
+        <v>143</v>
+      </c>
+      <c r="M15" s="40"/>
+      <c r="N15" s="18"/>
+      <c r="O15" s="29" t="s">
+        <v>144</v>
+      </c>
+      <c r="P15" s="41"/>
+    </row>
+    <row r="16" spans="1:29" ht="33" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A16" s="21"/>
-      <c r="B16" s="45" t="s">
-        <v>202</v>
-      </c>
+      <c r="B16" s="50"/>
       <c r="C16" s="6" t="s">
-        <v>256</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>203</v>
-      </c>
-      <c r="E16" s="6"/>
-      <c r="F16" s="6"/>
-      <c r="G16" s="6"/>
-      <c r="H16" s="6"/>
-      <c r="I16" s="16"/>
-      <c r="J16" s="19" t="s">
-        <v>242</v>
-      </c>
-      <c r="K16" s="52" t="s">
-        <v>204</v>
-      </c>
-      <c r="L16" s="19" t="s">
         <v>205</v>
       </c>
-      <c r="M16" s="51"/>
-      <c r="N16" s="18"/>
-      <c r="O16" s="30" t="s">
-        <v>206</v>
-      </c>
-      <c r="P16" s="49"/>
+      <c r="D16" s="35" t="s">
+        <v>145</v>
+      </c>
+      <c r="E16" s="21"/>
+      <c r="F16" s="21"/>
+      <c r="G16" s="21"/>
+      <c r="H16" s="21"/>
+      <c r="I16" s="36"/>
+      <c r="J16" s="37" t="s">
+        <v>146</v>
+      </c>
+      <c r="K16" s="36" t="s">
+        <v>147</v>
+      </c>
+      <c r="L16" s="37" t="s">
+        <v>148</v>
+      </c>
+      <c r="M16" s="18"/>
+      <c r="N16" s="38"/>
+      <c r="O16" s="31" t="s">
+        <v>149</v>
+      </c>
+      <c r="P16" s="42"/>
       <c r="Q16"/>
       <c r="R16"/>
       <c r="S16"/>
@@ -2429,14 +2260,16 @@
       <c r="AB16"/>
       <c r="AC16"/>
     </row>
-    <row r="17" spans="1:29" ht="33" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="36"/>
-      <c r="B17" s="46"/>
+    <row r="17" spans="1:29" ht="33" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A17" s="21"/>
+      <c r="B17" s="48" t="s">
+        <v>152</v>
+      </c>
       <c r="C17" s="6" t="s">
-        <v>257</v>
+        <v>206</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>207</v>
+        <v>153</v>
       </c>
       <c r="E17" s="6"/>
       <c r="F17" s="6"/>
@@ -2444,20 +2277,20 @@
       <c r="H17" s="6"/>
       <c r="I17" s="16"/>
       <c r="J17" s="19" t="s">
-        <v>208</v>
-      </c>
-      <c r="K17" s="16" t="s">
-        <v>249</v>
+        <v>192</v>
+      </c>
+      <c r="K17" s="44" t="s">
+        <v>154</v>
       </c>
       <c r="L17" s="19" t="s">
-        <v>250</v>
-      </c>
-      <c r="M17" s="18"/>
+        <v>155</v>
+      </c>
+      <c r="M17" s="43"/>
       <c r="N17" s="18"/>
-      <c r="O17" s="30" t="s">
-        <v>209</v>
-      </c>
-      <c r="P17" s="49"/>
+      <c r="O17" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="P17" s="41"/>
       <c r="Q17"/>
       <c r="R17"/>
       <c r="S17"/>
@@ -2472,14 +2305,14 @@
       <c r="AB17"/>
       <c r="AC17"/>
     </row>
-    <row r="18" spans="1:29" ht="33" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="36"/>
-      <c r="B18" s="47"/>
+    <row r="18" spans="1:29" ht="33" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A18" s="21"/>
+      <c r="B18" s="49"/>
       <c r="C18" s="6" t="s">
-        <v>258</v>
+        <v>207</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>210</v>
+        <v>157</v>
       </c>
       <c r="E18" s="6"/>
       <c r="F18" s="6"/>
@@ -2487,20 +2320,20 @@
       <c r="H18" s="6"/>
       <c r="I18" s="16"/>
       <c r="J18" s="19" t="s">
-        <v>211</v>
-      </c>
-      <c r="K18" s="52" t="s">
-        <v>251</v>
+        <v>158</v>
+      </c>
+      <c r="K18" s="16" t="s">
+        <v>199</v>
       </c>
       <c r="L18" s="19" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="M18" s="18"/>
       <c r="N18" s="18"/>
-      <c r="O18" s="30" t="s">
-        <v>213</v>
-      </c>
-      <c r="P18" s="49"/>
+      <c r="O18" s="29" t="s">
+        <v>159</v>
+      </c>
+      <c r="P18" s="41"/>
       <c r="Q18"/>
       <c r="R18"/>
       <c r="S18"/>
@@ -2515,41 +2348,35 @@
       <c r="AB18"/>
       <c r="AC18"/>
     </row>
-    <row r="19" spans="1:29" ht="35.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:29" ht="35.15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A19" s="21"/>
-      <c r="B19" s="42" t="s">
-        <v>200</v>
-      </c>
+      <c r="B19" s="50"/>
       <c r="C19" s="6" t="s">
-        <v>259</v>
-      </c>
-      <c r="D19" s="24" t="s">
-        <v>161</v>
+        <v>208</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>160</v>
       </c>
       <c r="E19" s="6"/>
       <c r="F19" s="6"/>
       <c r="G19" s="6"/>
       <c r="H19" s="6"/>
-      <c r="I19" s="33" t="s">
-        <v>59</v>
-      </c>
-      <c r="J19" s="26" t="s">
-        <v>214</v>
-      </c>
-      <c r="K19" s="33" t="s">
+      <c r="I19" s="16"/>
+      <c r="J19" s="19" t="s">
+        <v>161</v>
+      </c>
+      <c r="K19" s="44" t="s">
+        <v>201</v>
+      </c>
+      <c r="L19" s="19" t="s">
         <v>162</v>
       </c>
-      <c r="L19" s="25" t="s">
-        <v>215</v>
-      </c>
-      <c r="M19" s="35" t="s">
-        <v>189</v>
-      </c>
-      <c r="N19" s="2"/>
-      <c r="O19" s="34" t="s">
-        <v>216</v>
-      </c>
-      <c r="P19" s="2"/>
+      <c r="M19" s="18"/>
+      <c r="N19" s="18"/>
+      <c r="O19" s="29" t="s">
+        <v>163</v>
+      </c>
+      <c r="P19" s="41"/>
       <c r="Q19"/>
       <c r="R19"/>
       <c r="S19"/>
@@ -2564,693 +2391,512 @@
       <c r="AB19"/>
       <c r="AC19"/>
     </row>
-    <row r="20" spans="1:29" ht="120" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:29" ht="116" x14ac:dyDescent="0.45">
       <c r="A20" s="27"/>
-      <c r="B20" s="43"/>
+      <c r="B20" s="45" t="s">
+        <v>150</v>
+      </c>
       <c r="C20" s="6" t="s">
-        <v>260</v>
+        <v>209</v>
       </c>
       <c r="D20" s="24" t="s">
-        <v>54</v>
+        <v>111</v>
       </c>
       <c r="E20" s="6"/>
       <c r="F20" s="6"/>
       <c r="G20" s="6"/>
       <c r="H20" s="6"/>
-      <c r="I20" s="33" t="s">
-        <v>60</v>
+      <c r="I20" s="32" t="s">
+        <v>55</v>
       </c>
       <c r="J20" s="26" t="s">
-        <v>217</v>
-      </c>
-      <c r="K20" s="33" t="s">
-        <v>218</v>
+        <v>164</v>
+      </c>
+      <c r="K20" s="32" t="s">
+        <v>112</v>
       </c>
       <c r="L20" s="25" t="s">
-        <v>219</v>
-      </c>
-      <c r="M20" s="35" t="s">
-        <v>65</v>
+        <v>165</v>
+      </c>
+      <c r="M20" s="34" t="s">
+        <v>139</v>
       </c>
       <c r="N20" s="2"/>
-      <c r="O20" s="34" t="s">
-        <v>163</v>
+      <c r="O20" s="33" t="s">
+        <v>166</v>
       </c>
       <c r="P20" s="2"/>
     </row>
-    <row r="21" spans="1:29" ht="32.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:29" ht="32.15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A21" s="27"/>
-      <c r="B21" s="43"/>
+      <c r="B21" s="46"/>
       <c r="C21" s="6" t="s">
-        <v>261</v>
+        <v>210</v>
       </c>
       <c r="D21" s="24" t="s">
-        <v>164</v>
+        <v>50</v>
       </c>
       <c r="E21" s="6"/>
       <c r="F21" s="6"/>
       <c r="G21" s="6"/>
       <c r="H21" s="6"/>
-      <c r="I21" s="33" t="s">
+      <c r="I21" s="32" t="s">
+        <v>56</v>
+      </c>
+      <c r="J21" s="26" t="s">
+        <v>167</v>
+      </c>
+      <c r="K21" s="32" t="s">
+        <v>168</v>
+      </c>
+      <c r="L21" s="25" t="s">
+        <v>169</v>
+      </c>
+      <c r="M21" s="34" t="s">
         <v>61</v>
       </c>
-      <c r="J21" s="26" t="s">
-        <v>247</v>
-      </c>
-      <c r="K21" s="33" t="s">
-        <v>246</v>
-      </c>
-      <c r="L21" s="25" t="s">
-        <v>165</v>
-      </c>
-      <c r="M21" s="35" t="s">
-        <v>66</v>
-      </c>
       <c r="N21" s="2"/>
-      <c r="O21" s="34" t="s">
-        <v>166</v>
+      <c r="O21" s="33" t="s">
+        <v>113</v>
       </c>
       <c r="P21" s="2"/>
     </row>
-    <row r="22" spans="1:29" ht="96" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:29" ht="145" x14ac:dyDescent="0.45">
       <c r="A22" s="27"/>
-      <c r="B22" s="43"/>
+      <c r="B22" s="46"/>
       <c r="C22" s="6" t="s">
-        <v>262</v>
+        <v>211</v>
       </c>
       <c r="D22" s="24" t="s">
-        <v>55</v>
+        <v>114</v>
       </c>
       <c r="E22" s="6"/>
       <c r="F22" s="6"/>
       <c r="G22" s="6"/>
       <c r="H22" s="6"/>
-      <c r="I22" s="33" t="s">
+      <c r="I22" s="32" t="s">
+        <v>57</v>
+      </c>
+      <c r="J22" s="26" t="s">
+        <v>197</v>
+      </c>
+      <c r="K22" s="32" t="s">
+        <v>196</v>
+      </c>
+      <c r="L22" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="M22" s="34" t="s">
         <v>62</v>
       </c>
-      <c r="J22" s="26" t="s">
-        <v>245</v>
-      </c>
-      <c r="K22" s="33" t="s">
-        <v>220</v>
-      </c>
-      <c r="L22" s="25" t="s">
-        <v>221</v>
-      </c>
-      <c r="M22" s="35" t="s">
-        <v>67</v>
-      </c>
       <c r="N22" s="2"/>
-      <c r="O22" s="34" t="s">
-        <v>167</v>
+      <c r="O22" s="33" t="s">
+        <v>116</v>
       </c>
       <c r="P22" s="2"/>
     </row>
-    <row r="23" spans="1:29" ht="144" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:29" ht="116" x14ac:dyDescent="0.45">
       <c r="A23" s="27"/>
-      <c r="B23" s="43"/>
+      <c r="B23" s="46"/>
       <c r="C23" s="6" t="s">
-        <v>263</v>
+        <v>212</v>
       </c>
       <c r="D23" s="24" t="s">
-        <v>168</v>
+        <v>51</v>
       </c>
       <c r="E23" s="6"/>
       <c r="F23" s="6"/>
       <c r="G23" s="6"/>
       <c r="H23" s="6"/>
-      <c r="I23" s="33" t="s">
-        <v>64</v>
+      <c r="I23" s="32" t="s">
+        <v>58</v>
       </c>
       <c r="J23" s="26" t="s">
-        <v>244</v>
-      </c>
-      <c r="K23" s="33" t="s">
-        <v>243</v>
+        <v>195</v>
+      </c>
+      <c r="K23" s="32" t="s">
+        <v>170</v>
       </c>
       <c r="L23" s="25" t="s">
-        <v>222</v>
-      </c>
-      <c r="M23" s="35"/>
+        <v>171</v>
+      </c>
+      <c r="M23" s="34" t="s">
+        <v>63</v>
+      </c>
       <c r="N23" s="2"/>
-      <c r="O23" s="34" t="s">
-        <v>169</v>
+      <c r="O23" s="33" t="s">
+        <v>117</v>
       </c>
       <c r="P23" s="2"/>
     </row>
-    <row r="24" spans="1:29" ht="162" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:29" ht="174" x14ac:dyDescent="0.45">
       <c r="A24" s="27"/>
-      <c r="B24" s="43"/>
+      <c r="B24" s="46"/>
       <c r="C24" s="6" t="s">
-        <v>264</v>
+        <v>213</v>
       </c>
       <c r="D24" s="24" t="s">
-        <v>56</v>
+        <v>118</v>
       </c>
       <c r="E24" s="6"/>
       <c r="F24" s="6"/>
       <c r="G24" s="6"/>
       <c r="H24" s="6"/>
-      <c r="I24" s="33" t="s">
-        <v>63</v>
+      <c r="I24" s="32" t="s">
+        <v>60</v>
       </c>
       <c r="J24" s="26" t="s">
-        <v>223</v>
-      </c>
-      <c r="K24" s="33" t="s">
-        <v>224</v>
+        <v>194</v>
+      </c>
+      <c r="K24" s="32" t="s">
+        <v>193</v>
       </c>
       <c r="L24" s="25" t="s">
-        <v>225</v>
-      </c>
-      <c r="M24" s="35"/>
+        <v>172</v>
+      </c>
+      <c r="M24" s="34"/>
       <c r="N24" s="2"/>
-      <c r="O24" s="34" t="s">
-        <v>68</v>
+      <c r="O24" s="33" t="s">
+        <v>119</v>
       </c>
       <c r="P24" s="2"/>
     </row>
-    <row r="25" spans="1:29" ht="81" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:29" ht="192" x14ac:dyDescent="0.45">
       <c r="A25" s="27"/>
-      <c r="B25" s="43"/>
+      <c r="B25" s="46"/>
       <c r="C25" s="6" t="s">
-        <v>46</v>
+        <v>214</v>
       </c>
       <c r="D25" s="24" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="E25" s="6"/>
       <c r="F25" s="6"/>
       <c r="G25" s="6"/>
       <c r="H25" s="6"/>
-      <c r="I25" s="33" t="s">
-        <v>69</v>
+      <c r="I25" s="32" t="s">
+        <v>59</v>
       </c>
       <c r="J25" s="26" t="s">
-        <v>226</v>
-      </c>
-      <c r="K25" s="33" t="s">
-        <v>171</v>
+        <v>173</v>
+      </c>
+      <c r="K25" s="32" t="s">
+        <v>174</v>
       </c>
       <c r="L25" s="25" t="s">
-        <v>227</v>
-      </c>
-      <c r="M25" s="35"/>
+        <v>175</v>
+      </c>
+      <c r="M25" s="34"/>
       <c r="N25" s="2"/>
-      <c r="O25" s="34" t="s">
-        <v>172</v>
+      <c r="O25" s="33" t="s">
+        <v>64</v>
       </c>
       <c r="P25" s="2"/>
     </row>
-    <row r="26" spans="1:29" ht="94.5" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:29" ht="96" x14ac:dyDescent="0.45">
       <c r="A26" s="27"/>
-      <c r="B26" s="44"/>
+      <c r="B26" s="46"/>
       <c r="C26" s="6" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="D26" s="24" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="E26" s="6"/>
       <c r="F26" s="6"/>
       <c r="G26" s="6"/>
       <c r="H26" s="6"/>
-      <c r="I26" s="33" t="s">
-        <v>70</v>
+      <c r="I26" s="32" t="s">
+        <v>65</v>
       </c>
       <c r="J26" s="26" t="s">
-        <v>228</v>
-      </c>
-      <c r="K26" s="33" t="s">
-        <v>173</v>
+        <v>176</v>
+      </c>
+      <c r="K26" s="32" t="s">
+        <v>121</v>
       </c>
       <c r="L26" s="25" t="s">
-        <v>229</v>
-      </c>
-      <c r="M26" s="35"/>
+        <v>177</v>
+      </c>
+      <c r="M26" s="34"/>
       <c r="N26" s="2"/>
-      <c r="O26" s="34" t="s">
-        <v>174</v>
+      <c r="O26" s="33" t="s">
+        <v>122</v>
       </c>
       <c r="P26" s="2"/>
     </row>
-    <row r="27" spans="1:29" ht="36" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:29" ht="112" x14ac:dyDescent="0.45">
       <c r="A27" s="27"/>
-      <c r="B27" s="42" t="s">
-        <v>71</v>
-      </c>
+      <c r="B27" s="47"/>
       <c r="C27" s="6" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="D27" s="24" t="s">
-        <v>76</v>
+        <v>54</v>
       </c>
       <c r="E27" s="6"/>
       <c r="F27" s="6"/>
       <c r="G27" s="6"/>
       <c r="H27" s="6"/>
-      <c r="I27" s="33" t="s">
-        <v>80</v>
+      <c r="I27" s="32" t="s">
+        <v>66</v>
       </c>
       <c r="J27" s="26" t="s">
-        <v>81</v>
-      </c>
-      <c r="K27" s="33" t="s">
-        <v>170</v>
-      </c>
-      <c r="L27" s="25"/>
-      <c r="M27" s="35" t="s">
-        <v>82</v>
-      </c>
+        <v>178</v>
+      </c>
+      <c r="K27" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="L27" s="25" t="s">
+        <v>179</v>
+      </c>
+      <c r="M27" s="34"/>
       <c r="N27" s="2"/>
-      <c r="O27" s="34" t="s">
-        <v>83</v>
+      <c r="O27" s="33" t="s">
+        <v>124</v>
       </c>
       <c r="P27" s="2"/>
     </row>
-    <row r="28" spans="1:29" ht="27" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:29" ht="43.5" x14ac:dyDescent="0.45">
       <c r="A28" s="27"/>
-      <c r="B28" s="43"/>
+      <c r="B28" s="45" t="s">
+        <v>67</v>
+      </c>
       <c r="C28" s="6" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="D28" s="24" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="E28" s="6"/>
       <c r="F28" s="6"/>
       <c r="G28" s="6"/>
       <c r="H28" s="6"/>
-      <c r="I28" s="33" t="s">
-        <v>84</v>
+      <c r="I28" s="32" t="s">
+        <v>73</v>
       </c>
       <c r="J28" s="26" t="s">
-        <v>85</v>
-      </c>
-      <c r="K28" s="33" t="s">
-        <v>86</v>
-      </c>
-      <c r="L28" s="25" t="s">
-        <v>87</v>
-      </c>
-      <c r="M28" s="35"/>
-      <c r="N28" s="35"/>
-      <c r="O28" s="34" t="s">
-        <v>88</v>
+        <v>74</v>
+      </c>
+      <c r="K28" s="32" t="s">
+        <v>120</v>
+      </c>
+      <c r="L28" s="25"/>
+      <c r="M28" s="34" t="s">
+        <v>75</v>
+      </c>
+      <c r="N28" s="2"/>
+      <c r="O28" s="33" t="s">
+        <v>76</v>
       </c>
       <c r="P28" s="2"/>
     </row>
-    <row r="29" spans="1:29" ht="27" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:29" ht="32" x14ac:dyDescent="0.45">
       <c r="A29" s="27"/>
-      <c r="B29" s="43"/>
+      <c r="B29" s="46"/>
       <c r="C29" s="6" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="D29" s="24" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="E29" s="6"/>
       <c r="F29" s="6"/>
       <c r="G29" s="6"/>
       <c r="H29" s="6"/>
-      <c r="I29" s="33" t="s">
-        <v>89</v>
+      <c r="I29" s="32" t="s">
+        <v>77</v>
       </c>
       <c r="J29" s="26" t="s">
-        <v>90</v>
-      </c>
-      <c r="K29" s="33" t="s">
-        <v>91</v>
+        <v>78</v>
+      </c>
+      <c r="K29" s="32" t="s">
+        <v>79</v>
       </c>
       <c r="L29" s="25" t="s">
-        <v>92</v>
-      </c>
-      <c r="M29" s="35"/>
-      <c r="N29" s="2"/>
-      <c r="O29" s="34" t="s">
-        <v>93</v>
+        <v>80</v>
+      </c>
+      <c r="M29" s="34"/>
+      <c r="N29" s="34"/>
+      <c r="O29" s="33" t="s">
+        <v>81</v>
       </c>
       <c r="P29" s="2"/>
     </row>
-    <row r="30" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:29" ht="32" x14ac:dyDescent="0.45">
       <c r="A30" s="27"/>
-      <c r="B30" s="44"/>
+      <c r="B30" s="46"/>
       <c r="C30" s="6" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="D30" s="24" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="E30" s="6"/>
       <c r="F30" s="6"/>
       <c r="G30" s="6"/>
       <c r="H30" s="6"/>
-      <c r="I30" s="33" t="s">
-        <v>94</v>
+      <c r="I30" s="32" t="s">
+        <v>82</v>
       </c>
       <c r="J30" s="26" t="s">
-        <v>95</v>
-      </c>
-      <c r="K30" s="33" t="s">
-        <v>96</v>
+        <v>83</v>
+      </c>
+      <c r="K30" s="32" t="s">
+        <v>84</v>
       </c>
       <c r="L30" s="25" t="s">
-        <v>97</v>
-      </c>
-      <c r="M30" s="35"/>
+        <v>85</v>
+      </c>
+      <c r="M30" s="34"/>
       <c r="N30" s="2"/>
-      <c r="O30" s="34" t="s">
-        <v>98</v>
+      <c r="O30" s="33" t="s">
+        <v>86</v>
       </c>
       <c r="P30" s="2"/>
     </row>
-    <row r="31" spans="1:29" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:29" ht="26.15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A31" s="27"/>
-      <c r="B31" s="42" t="s">
-        <v>99</v>
-      </c>
+      <c r="B31" s="47"/>
       <c r="C31" s="6" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="D31" s="24" t="s">
-        <v>103</v>
+        <v>72</v>
       </c>
       <c r="E31" s="6"/>
       <c r="F31" s="6"/>
       <c r="G31" s="6"/>
       <c r="H31" s="6"/>
-      <c r="I31" s="33" t="s">
-        <v>106</v>
+      <c r="I31" s="32" t="s">
+        <v>87</v>
       </c>
       <c r="J31" s="26" t="s">
-        <v>107</v>
-      </c>
-      <c r="K31" s="33" t="s">
-        <v>108</v>
+        <v>88</v>
+      </c>
+      <c r="K31" s="32" t="s">
+        <v>89</v>
       </c>
       <c r="L31" s="25" t="s">
-        <v>109</v>
-      </c>
-      <c r="M31" s="35"/>
+        <v>90</v>
+      </c>
+      <c r="M31" s="34"/>
       <c r="N31" s="2"/>
-      <c r="O31" s="34" t="s">
-        <v>110</v>
+      <c r="O31" s="33" t="s">
+        <v>91</v>
       </c>
       <c r="P31" s="2"/>
     </row>
-    <row r="32" spans="1:29" ht="29.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:29" ht="29.15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A32" s="27"/>
-      <c r="B32" s="43"/>
+      <c r="B32" s="45" t="s">
+        <v>92</v>
+      </c>
       <c r="C32" s="6" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="D32" s="24" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="E32" s="6"/>
       <c r="F32" s="6"/>
       <c r="G32" s="6"/>
       <c r="H32" s="6"/>
-      <c r="I32" s="33" t="s">
-        <v>111</v>
+      <c r="I32" s="32" t="s">
+        <v>96</v>
       </c>
       <c r="J32" s="26" t="s">
-        <v>112</v>
-      </c>
-      <c r="K32" s="33" t="s">
-        <v>113</v>
+        <v>97</v>
+      </c>
+      <c r="K32" s="32" t="s">
+        <v>98</v>
       </c>
       <c r="L32" s="25" t="s">
-        <v>114</v>
-      </c>
-      <c r="M32" s="35"/>
+        <v>99</v>
+      </c>
+      <c r="M32" s="34"/>
       <c r="N32" s="2"/>
-      <c r="O32" s="34" t="s">
-        <v>115</v>
+      <c r="O32" s="33" t="s">
+        <v>100</v>
       </c>
       <c r="P32" s="2"/>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A33" s="27"/>
-      <c r="B33" s="44"/>
+    <row r="33" spans="1:16" ht="48" x14ac:dyDescent="0.45">
+      <c r="A33" s="39"/>
+      <c r="B33" s="46"/>
       <c r="C33" s="6" t="s">
-        <v>72</v>
+        <v>49</v>
       </c>
       <c r="D33" s="24" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="E33" s="6"/>
       <c r="F33" s="6"/>
       <c r="G33" s="6"/>
       <c r="H33" s="6"/>
-      <c r="I33" s="33" t="s">
-        <v>117</v>
+      <c r="I33" s="32" t="s">
+        <v>101</v>
       </c>
       <c r="J33" s="26" t="s">
-        <v>118</v>
-      </c>
-      <c r="K33" s="33" t="s">
-        <v>119</v>
+        <v>102</v>
+      </c>
+      <c r="K33" s="32" t="s">
+        <v>103</v>
       </c>
       <c r="L33" s="25" t="s">
-        <v>120</v>
-      </c>
-      <c r="M33" s="35"/>
+        <v>104</v>
+      </c>
+      <c r="M33" s="34"/>
       <c r="N33" s="2"/>
-      <c r="O33" s="34" t="s">
-        <v>116</v>
+      <c r="O33" s="33" t="s">
+        <v>105</v>
       </c>
       <c r="P33" s="2"/>
     </row>
-    <row r="34" spans="1:16" ht="27" x14ac:dyDescent="0.3">
-      <c r="A34" s="27"/>
-      <c r="B34" s="42" t="s">
-        <v>121</v>
-      </c>
+    <row r="34" spans="1:16" ht="33" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B34" s="47"/>
       <c r="C34" s="6" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="D34" s="24" t="s">
-        <v>122</v>
+        <v>95</v>
       </c>
       <c r="E34" s="6"/>
       <c r="F34" s="6"/>
       <c r="G34" s="6"/>
       <c r="H34" s="6"/>
-      <c r="I34" s="33" t="s">
-        <v>123</v>
+      <c r="I34" s="32" t="s">
+        <v>107</v>
       </c>
       <c r="J34" s="26" t="s">
-        <v>124</v>
-      </c>
-      <c r="K34" s="33" t="s">
-        <v>125</v>
+        <v>108</v>
+      </c>
+      <c r="K34" s="32" t="s">
+        <v>109</v>
       </c>
       <c r="L34" s="25" t="s">
-        <v>126</v>
-      </c>
-      <c r="M34" s="35" t="s">
-        <v>127</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="M34" s="34"/>
       <c r="N34" s="2"/>
-      <c r="O34" s="34" t="s">
-        <v>128</v>
+      <c r="O34" s="33" t="s">
+        <v>106</v>
       </c>
       <c r="P34" s="2"/>
     </row>
-    <row r="35" spans="1:16" ht="27" x14ac:dyDescent="0.3">
-      <c r="A35" s="27"/>
-      <c r="B35" s="43"/>
-      <c r="C35" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="D35" s="24" t="s">
-        <v>129</v>
-      </c>
-      <c r="E35" s="6"/>
-      <c r="F35" s="6"/>
-      <c r="G35" s="6"/>
-      <c r="H35" s="6"/>
-      <c r="I35" s="33" t="s">
-        <v>130</v>
-      </c>
-      <c r="J35" s="26" t="s">
-        <v>131</v>
-      </c>
-      <c r="K35" s="33" t="s">
-        <v>132</v>
-      </c>
-      <c r="L35" s="25" t="s">
-        <v>133</v>
-      </c>
-      <c r="M35" s="35" t="s">
-        <v>134</v>
-      </c>
-      <c r="N35" s="2"/>
-      <c r="O35" s="34" t="s">
-        <v>135</v>
-      </c>
-      <c r="P35" s="2"/>
-    </row>
-    <row r="36" spans="1:16" ht="30.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="27"/>
-      <c r="B36" s="43"/>
-      <c r="C36" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="D36" s="24" t="s">
-        <v>136</v>
-      </c>
-      <c r="E36" s="6"/>
-      <c r="F36" s="6"/>
-      <c r="G36" s="6"/>
-      <c r="H36" s="6"/>
-      <c r="I36" s="33" t="s">
-        <v>137</v>
-      </c>
-      <c r="J36" s="26" t="s">
-        <v>138</v>
-      </c>
-      <c r="K36" s="33" t="s">
-        <v>139</v>
-      </c>
-      <c r="L36" s="25" t="s">
-        <v>140</v>
-      </c>
-      <c r="M36" s="35" t="s">
-        <v>142</v>
-      </c>
-      <c r="N36" s="2"/>
-      <c r="O36" s="34" t="s">
-        <v>141</v>
-      </c>
-      <c r="P36" s="2"/>
-    </row>
-    <row r="37" spans="1:16" ht="36" x14ac:dyDescent="0.3">
-      <c r="A37" s="27"/>
-      <c r="B37" s="42" t="s">
-        <v>143</v>
-      </c>
-      <c r="C37" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="D37" s="24" t="s">
-        <v>144</v>
-      </c>
-      <c r="E37" s="6"/>
-      <c r="F37" s="6"/>
-      <c r="G37" s="6"/>
-      <c r="H37" s="6"/>
-      <c r="I37" s="33"/>
-      <c r="J37" s="26" t="s">
-        <v>145</v>
-      </c>
-      <c r="K37" s="33" t="s">
-        <v>146</v>
-      </c>
-      <c r="L37" s="25" t="s">
-        <v>147</v>
-      </c>
-      <c r="M37" s="35"/>
-      <c r="N37" s="2"/>
-      <c r="O37" s="34" t="s">
-        <v>148</v>
-      </c>
-      <c r="P37" s="2"/>
-    </row>
-    <row r="38" spans="1:16" ht="24" x14ac:dyDescent="0.3">
-      <c r="A38" s="27"/>
-      <c r="B38" s="43"/>
-      <c r="C38" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="D38" s="24" t="s">
-        <v>152</v>
-      </c>
-      <c r="E38" s="6"/>
-      <c r="F38" s="6"/>
-      <c r="G38" s="6"/>
-      <c r="H38" s="6"/>
-      <c r="I38" s="33" t="s">
-        <v>149</v>
-      </c>
-      <c r="J38" s="26" t="s">
-        <v>153</v>
-      </c>
-      <c r="K38" s="33" t="s">
-        <v>155</v>
-      </c>
-      <c r="L38" s="25" t="s">
-        <v>157</v>
-      </c>
-      <c r="M38" s="35"/>
-      <c r="N38" s="2"/>
-      <c r="O38" s="34" t="s">
-        <v>159</v>
-      </c>
-      <c r="P38" s="2"/>
-    </row>
-    <row r="39" spans="1:16" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="27"/>
-      <c r="B39" s="44"/>
-      <c r="C39" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="D39" s="24" t="s">
-        <v>151</v>
-      </c>
-      <c r="E39" s="6"/>
-      <c r="F39" s="6"/>
-      <c r="G39" s="6"/>
-      <c r="H39" s="6"/>
-      <c r="I39" s="33" t="s">
-        <v>150</v>
-      </c>
-      <c r="J39" s="26" t="s">
-        <v>154</v>
-      </c>
-      <c r="K39" s="33" t="s">
-        <v>156</v>
-      </c>
-      <c r="L39" s="25" t="s">
-        <v>158</v>
-      </c>
-      <c r="M39" s="35"/>
-      <c r="N39" s="2"/>
-      <c r="O39" s="34" t="s">
-        <v>160</v>
-      </c>
-      <c r="P39" s="2"/>
-    </row>
-    <row r="40" spans="1:16" ht="33" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="27"/>
-    </row>
-    <row r="41" spans="1:16" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="27"/>
-    </row>
-    <row r="42" spans="1:16" ht="45.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="27"/>
-    </row>
-    <row r="43" spans="1:16" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="27"/>
-    </row>
-    <row r="44" spans="1:16" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="27"/>
-    </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A45" s="28"/>
-    </row>
+    <row r="35" spans="1:16" ht="34" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="36" spans="1:16" ht="46" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="37" spans="1:16" ht="34" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="38" spans="1:16" ht="34" customHeight="1" x14ac:dyDescent="0.45"/>
   </sheetData>
-  <mergeCells count="9">
-    <mergeCell ref="B37:B39"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="B19:B26"/>
-    <mergeCell ref="B27:B30"/>
-    <mergeCell ref="B31:B33"/>
-    <mergeCell ref="B34:B36"/>
-    <mergeCell ref="B16:B18"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="B11:B13"/>
+  <mergeCells count="7">
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="B20:B27"/>
+    <mergeCell ref="B28:B31"/>
+    <mergeCell ref="B32:B34"/>
+    <mergeCell ref="B17:B19"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="B12:B14"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
